--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_34.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_34.xlsx
@@ -471,98 +471,98 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85922</v>
+        <v>28965</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr. Kaique Melo</t>
+          <t>Guilherme da Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45078</v>
+        <v>45096</v>
       </c>
       <c r="G2" t="n">
-        <v>4949.91</v>
+        <v>10117.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>29466</v>
+        <v>11280</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Benício da Conceição</t>
+          <t>Alana Ramos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45082</v>
+        <v>45102</v>
       </c>
       <c r="G3" t="n">
-        <v>10806.39</v>
+        <v>5397.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>44052</v>
+        <v>84455</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Isabelly da Cruz</t>
+          <t>Renan Nogueira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="G4" t="n">
-        <v>10974.29</v>
+        <v>3287.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50257</v>
+        <v>1715</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcelo Fogaça</t>
+          <t>Kevin Mendes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45091</v>
+        <v>45088</v>
       </c>
       <c r="G5" t="n">
-        <v>3239.88</v>
+        <v>8098.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>580</v>
+        <v>1515</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Davi Lucas Vieira</t>
+          <t>Luigi Nascimento</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,31 +601,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45087</v>
+        <v>45082</v>
       </c>
       <c r="G6" t="n">
-        <v>5077.3</v>
+        <v>5393.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85480</v>
+        <v>87649</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arthur da Cruz</t>
+          <t>Dr. Lucca Azevedo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -634,56 +634,56 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45081</v>
+        <v>45089</v>
       </c>
       <c r="G7" t="n">
-        <v>12289.86</v>
+        <v>4706.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48336</v>
+        <v>59950</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dra. Isis da Rocha</t>
+          <t>Srta. Camila Pereira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45084</v>
+        <v>45091</v>
       </c>
       <c r="G8" t="n">
-        <v>3889.93</v>
+        <v>4486.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86146</v>
+        <v>78763</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ana Sophia Caldeira</t>
+          <t>Kevin Monteiro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -692,71 +692,71 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45091</v>
+        <v>45095</v>
       </c>
       <c r="G9" t="n">
-        <v>7654.28</v>
+        <v>9013.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8033</v>
+        <v>25809</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Julia da Luz</t>
+          <t>Sra. Emanuella da Cunha</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45103</v>
+        <v>45106</v>
       </c>
       <c r="G10" t="n">
-        <v>5443.32</v>
+        <v>7492.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>59853</v>
+        <v>41697</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calebe Barros</t>
+          <t>Pedro Miguel Rodrigues</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45079</v>
+        <v>45080</v>
       </c>
       <c r="G11" t="n">
-        <v>4760.03</v>
+        <v>8454.709999999999</v>
       </c>
     </row>
   </sheetData>
